--- a/行動予定表_1101.xlsx
+++ b/行動予定表_1101.xlsx
@@ -1208,7 +1208,7 @@
     <row r="22" ht="22.05" customHeight="1" s="28">
       <c r="A22" s="51" t="inlineStr">
         <is>
-          <t>15:00　案件整理</t>
+          <t>15:00　案件整理（古澤様のお父様の住み替え先の選定）</t>
         </is>
       </c>
       <c r="B22" s="13" t="n"/>
@@ -1226,7 +1226,7 @@
     <row r="23" ht="22.05" customHeight="1" s="28">
       <c r="A23" s="51" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・住み替え一覧(お父様)を仕上げ、17:00までに社長へ送る（11/2お届け分）</t>
+          <t xml:space="preserve">　・住み替え4件を比べて一覧を仕上げ、17:00までに社長へ送る（11/2に見積書と一緒にお届け）</t>
         </is>
       </c>
       <c r="B23" s="13" t="n"/>
